--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80602</v>
+        <v>80603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80603</v>
+        <v>80605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80605</v>
+        <v>80608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80608</v>
+        <v>80621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80621</v>
+        <v>80623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33320-2026 artfynd.xlsx
+++ b/artfynd/A 33320-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136703515</v>
       </c>
       <c r="B2" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
